--- a/14-automacao_tarefas/files/juntar_planilhas.xlsx
+++ b/14-automacao_tarefas/files/juntar_planilhas.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gastos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="teste" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gastos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,9 +414,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lucro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -428,82 +490,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Lucro</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Custos</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
